--- a/data/arabidopsis_datasets_info.xlsx
+++ b/data/arabidopsis_datasets_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luisabender/Studium/bachelor-thesis-luisa/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995BEECE-BB4A-E346-BB83-0882B1629A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE01838-0C60-FD47-A066-A27BC9C1D53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="3" xr2:uid="{78A52BC2-B19E-8341-BEF5-6A261385676E}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17360" xr2:uid="{78A52BC2-B19E-8341-BEF5-6A261385676E}"/>
   </bookViews>
   <sheets>
     <sheet name="biotrophic" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="472">
   <si>
     <t>Pathogen</t>
   </si>
@@ -1454,6 +1454,12 @@
   </si>
   <si>
     <t>3_9</t>
+  </si>
+  <si>
+    <t>biotroph, mesophyll (leaf) - removed during preprocessing</t>
+  </si>
+  <si>
+    <t>removed during preprocessing</t>
   </si>
 </sst>
 </file>
@@ -1514,7 +1520,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1524,6 +1530,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1541,7 +1553,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1581,12 +1593,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -2013,28 +2029,28 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="136" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="23" t="s">
         <v>436</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="24" t="s">
         <v>437</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H4" s="9" t="s">
+      <c r="F4" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="H4" s="22" t="s">
         <v>424</v>
       </c>
     </row>
@@ -2220,14 +2236,14 @@
         <v>420</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="22" customFormat="1" ht="153" x14ac:dyDescent="0.2">
-      <c r="A12" s="21" t="s">
+    <row r="12" spans="1:8" ht="153" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="4" t="s">
         <v>452</v>
       </c>
       <c r="D12" s="17" t="s">
@@ -2236,13 +2252,13 @@
       <c r="E12" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="H12" s="22" t="s">
+      <c r="G12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" t="s">
         <v>421</v>
       </c>
     </row>
@@ -2320,7 +2336,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="153" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -2346,7 +2362,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="153" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="85" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -2372,7 +2388,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="153" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="85" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -2398,7 +2414,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="238" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="119" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -2441,7 +2457,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247CB23F-CCA8-7344-8436-4F3475AB1487}">
-  <dimension ref="A1:G434"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -2449,6 +2465,7 @@
     <col min="3" max="3" width="23.1640625" customWidth="1"/>
     <col min="4" max="4" width="26.1640625" customWidth="1"/>
     <col min="5" max="6" width="15.33203125" customWidth="1"/>
+    <col min="8" max="8" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -3923,7 +3940,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="16" t="s">
         <v>104</v>
       </c>
@@ -3946,7 +3963,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="16" t="s">
         <v>105</v>
       </c>
@@ -3969,7 +3986,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="16" t="s">
         <v>106</v>
       </c>
@@ -3992,7 +4009,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="16" t="s">
         <v>107</v>
       </c>
@@ -4015,7 +4032,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="16" t="s">
         <v>108</v>
       </c>
@@ -4038,7 +4055,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="16" t="s">
         <v>109</v>
       </c>
@@ -4061,7 +4078,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="16" t="s">
         <v>110</v>
       </c>
@@ -4084,7 +4101,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="16" t="s">
         <v>111</v>
       </c>
@@ -4107,7 +4124,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="16" t="s">
         <v>112</v>
       </c>
@@ -4130,8 +4147,8 @@
         <v>421</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A74" s="24" t="s">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" s="16" t="s">
         <v>118</v>
       </c>
       <c r="B74" s="3" t="s">
@@ -4152,9 +4169,12 @@
       <c r="G74" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A75" s="24" t="s">
+      <c r="H74" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" s="16" t="s">
         <v>119</v>
       </c>
       <c r="B75" s="3" t="s">
@@ -4175,9 +4195,12 @@
       <c r="G75" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76" s="24" t="s">
+      <c r="H75" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76" s="16" t="s">
         <v>120</v>
       </c>
       <c r="B76" s="3" t="s">
@@ -4198,9 +4221,12 @@
       <c r="G76" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A77" s="24" t="s">
+      <c r="H76" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" s="16" t="s">
         <v>121</v>
       </c>
       <c r="B77" s="3" t="s">
@@ -4221,9 +4247,12 @@
       <c r="G77" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A78" s="24" t="s">
+      <c r="H77" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" s="16" t="s">
         <v>122</v>
       </c>
       <c r="B78" s="3" t="s">
@@ -4244,9 +4273,12 @@
       <c r="G78" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A79" s="24" t="s">
+      <c r="H78" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" s="16" t="s">
         <v>123</v>
       </c>
       <c r="B79" s="3" t="s">
@@ -4267,9 +4299,12 @@
       <c r="G79" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A80" s="24" t="s">
+      <c r="H79" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" s="16" t="s">
         <v>124</v>
       </c>
       <c r="B80" s="3" t="s">
@@ -4290,9 +4325,12 @@
       <c r="G80" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81" s="24" t="s">
+      <c r="H80" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81" s="16" t="s">
         <v>125</v>
       </c>
       <c r="B81" s="3" t="s">
@@ -4313,9 +4351,12 @@
       <c r="G81" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A82" s="24" t="s">
+      <c r="H81" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" s="16" t="s">
         <v>126</v>
       </c>
       <c r="B82" s="3" t="s">
@@ -4336,9 +4377,12 @@
       <c r="G82" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83" s="24" t="s">
+      <c r="H82" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" s="16" t="s">
         <v>127</v>
       </c>
       <c r="B83" s="3" t="s">
@@ -4359,9 +4403,12 @@
       <c r="G83" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84" s="24" t="s">
+      <c r="H83" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84" s="16" t="s">
         <v>128</v>
       </c>
       <c r="B84" s="3" t="s">
@@ -4382,9 +4429,12 @@
       <c r="G84" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" s="24" t="s">
+      <c r="H84" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85" s="16" t="s">
         <v>129</v>
       </c>
       <c r="B85" s="3" t="s">
@@ -4405,9 +4455,12 @@
       <c r="G85" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A86" s="24" t="s">
+      <c r="H85" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86" s="16" t="s">
         <v>130</v>
       </c>
       <c r="B86" s="3" t="s">
@@ -4428,9 +4481,12 @@
       <c r="G86" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A87" s="24" t="s">
+      <c r="H86" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87" s="16" t="s">
         <v>131</v>
       </c>
       <c r="B87" s="3" t="s">
@@ -4451,9 +4507,12 @@
       <c r="G87" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A88" s="24" t="s">
+      <c r="H87" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" s="16" t="s">
         <v>132</v>
       </c>
       <c r="B88" s="3" t="s">
@@ -4474,9 +4533,12 @@
       <c r="G88" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A89" s="24" t="s">
+      <c r="H88" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" s="16" t="s">
         <v>133</v>
       </c>
       <c r="B89" s="3" t="s">
@@ -4497,9 +4559,12 @@
       <c r="G89" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90" s="24" t="s">
+      <c r="H89" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90" s="16" t="s">
         <v>134</v>
       </c>
       <c r="B90" s="3" t="s">
@@ -4520,9 +4585,12 @@
       <c r="G90" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A91" s="24" t="s">
+      <c r="H90" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91" s="16" t="s">
         <v>135</v>
       </c>
       <c r="B91" s="3" t="s">
@@ -4543,8 +4611,11 @@
       <c r="G91" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H91" s="26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="16" t="s">
         <v>137</v>
       </c>
@@ -4567,7 +4638,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="16" t="s">
         <v>138</v>
       </c>
@@ -4590,7 +4661,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="16" t="s">
         <v>139</v>
       </c>
@@ -4613,7 +4684,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="16" t="s">
         <v>140</v>
       </c>
@@ -4636,7 +4707,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="16" t="s">
         <v>141</v>
       </c>
@@ -8409,7 +8480,7 @@
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A260" s="24" t="s">
+      <c r="A260" s="16" t="s">
         <v>319</v>
       </c>
       <c r="B260" t="s">
@@ -8432,7 +8503,7 @@
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A261" s="24" t="s">
+      <c r="A261" s="16" t="s">
         <v>323</v>
       </c>
       <c r="B261" t="s">
@@ -8455,7 +8526,7 @@
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A262" s="24" t="s">
+      <c r="A262" s="16" t="s">
         <v>324</v>
       </c>
       <c r="B262" t="s">
@@ -8478,7 +8549,7 @@
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A263" s="24" t="s">
+      <c r="A263" s="16" t="s">
         <v>325</v>
       </c>
       <c r="B263" t="s">
@@ -8501,7 +8572,7 @@
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A264" s="24" t="s">
+      <c r="A264" s="16" t="s">
         <v>326</v>
       </c>
       <c r="B264" t="s">
@@ -8524,7 +8595,7 @@
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A265" s="24" t="s">
+      <c r="A265" s="16" t="s">
         <v>327</v>
       </c>
       <c r="B265" t="s">
@@ -8547,7 +8618,7 @@
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A266" s="24" t="s">
+      <c r="A266" s="16" t="s">
         <v>328</v>
       </c>
       <c r="B266" t="s">
@@ -8570,7 +8641,7 @@
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A267" s="24" t="s">
+      <c r="A267" s="16" t="s">
         <v>329</v>
       </c>
       <c r="B267" t="s">
@@ -8593,7 +8664,7 @@
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A268" s="24" t="s">
+      <c r="A268" s="16" t="s">
         <v>330</v>
       </c>
       <c r="B268" t="s">
@@ -8616,7 +8687,7 @@
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A269" s="24" t="s">
+      <c r="A269" s="16" t="s">
         <v>331</v>
       </c>
       <c r="B269" t="s">
@@ -8639,7 +8710,7 @@
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A270" s="24" t="s">
+      <c r="A270" s="16" t="s">
         <v>332</v>
       </c>
       <c r="B270" t="s">
@@ -8662,7 +8733,7 @@
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A271" s="24" t="s">
+      <c r="A271" s="16" t="s">
         <v>333</v>
       </c>
       <c r="B271" t="s">
@@ -8685,7 +8756,7 @@
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A272" s="24" t="s">
+      <c r="A272" s="16" t="s">
         <v>334</v>
       </c>
       <c r="B272" t="s">
@@ -8708,7 +8779,7 @@
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A273" s="24" t="s">
+      <c r="A273" s="16" t="s">
         <v>335</v>
       </c>
       <c r="B273" t="s">
@@ -8731,7 +8802,7 @@
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A274" s="24" t="s">
+      <c r="A274" s="16" t="s">
         <v>336</v>
       </c>
       <c r="B274" t="s">
@@ -8754,7 +8825,7 @@
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A275" s="24" t="s">
+      <c r="A275" s="16" t="s">
         <v>337</v>
       </c>
       <c r="B275" t="s">
@@ -8777,7 +8848,7 @@
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A276" s="24" t="s">
+      <c r="A276" s="16" t="s">
         <v>338</v>
       </c>
       <c r="B276" t="s">
@@ -8800,7 +8871,7 @@
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A277" s="24" t="s">
+      <c r="A277" s="16" t="s">
         <v>339</v>
       </c>
       <c r="B277" t="s">
@@ -8823,7 +8894,7 @@
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A278" s="24" t="s">
+      <c r="A278" s="16" t="s">
         <v>340</v>
       </c>
       <c r="B278" t="s">
@@ -8846,7 +8917,7 @@
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A279" s="24" t="s">
+      <c r="A279" s="16" t="s">
         <v>351</v>
       </c>
       <c r="B279" t="s">
